--- a/public/files/products_export.xlsx
+++ b/public/files/products_export.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market Price</t>
   </si>
   <si>
     <t xml:space="preserve">Is Sub Qty</t>
@@ -198,7 +201,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,18 +236,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -289,32 +288,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -327,66 +330,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF38761D"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -395,7 +338,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>176760</xdr:colOff>
+      <xdr:colOff>177120</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>142920</xdr:rowOff>
     </xdr:from>
@@ -403,7 +346,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>597240</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>686880</xdr:rowOff>
+      <xdr:rowOff>686520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -416,8 +359,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="21464400">
-          <a:off x="1002960" y="331920"/>
-          <a:ext cx="420480" cy="543960"/>
+          <a:off x="977040" y="333360"/>
+          <a:ext cx="420120" cy="543600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -439,9 +382,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>434160</xdr:colOff>
+      <xdr:colOff>433800</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>417600</xdr:rowOff>
+      <xdr:rowOff>417240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -455,7 +398,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="885240" y="2182680"/>
-          <a:ext cx="349200" cy="320760"/>
+          <a:ext cx="348840" cy="320400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -477,9 +420,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>539280</xdr:colOff>
+      <xdr:colOff>538920</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>417600</xdr:rowOff>
+      <xdr:rowOff>417240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -493,7 +436,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="885600" y="2944800"/>
-          <a:ext cx="453960" cy="320760"/>
+          <a:ext cx="453600" cy="320400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -515,9 +458,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>336240</xdr:colOff>
+      <xdr:colOff>335880</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>319320</xdr:rowOff>
+      <xdr:rowOff>318960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -531,7 +474,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="796680" y="3907800"/>
-          <a:ext cx="339840" cy="320760"/>
+          <a:ext cx="339480" cy="320400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -724,367 +667,394 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="58.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="58.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="26" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="0"/>
+      <c r="AA1" s="0"/>
+      <c r="AB1" s="0"/>
+      <c r="AC1" s="0"/>
+      <c r="AD1" s="0"/>
+      <c r="AE1" s="0"/>
+      <c r="AF1" s="0"/>
+      <c r="AG1" s="0"/>
+      <c r="AH1" s="0"/>
+      <c r="AI1" s="0"/>
+      <c r="AJ1" s="0"/>
+      <c r="AK1" s="0"/>
+      <c r="AL1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>29384</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S2" s="2" t="n">
-        <v>174</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Y2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>38575</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>38575</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>279.99</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="V3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>299</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="83.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="A4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="I4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>8585858</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="W4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="X4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y4" s="1"/>
+      <c r="Y4" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="47" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="2" t="n">
+      <c r="A5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="G5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>75758858</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="5" t="n">
+        <f aca="false">K2*5%</f>
+        <v>5</v>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="W5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>30</v>
+      <c r="Y5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/public/files/products_export.xlsx
+++ b/public/files/products_export.xlsx
@@ -309,7 +309,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,15 +338,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>177120</xdr:colOff>
+      <xdr:colOff>315000</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>142920</xdr:rowOff>
+      <xdr:rowOff>57240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>597240</xdr:colOff>
+      <xdr:colOff>734760</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>686520</xdr:rowOff>
+      <xdr:rowOff>600480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -359,8 +359,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="21464400">
-          <a:off x="977040" y="333360"/>
-          <a:ext cx="420120" cy="543600"/>
+          <a:off x="1115280" y="247320"/>
+          <a:ext cx="419760" cy="543240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -376,15 +376,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>84960</xdr:colOff>
+      <xdr:colOff>320760</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>96840</xdr:rowOff>
+      <xdr:rowOff>163800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>433800</xdr:colOff>
+      <xdr:colOff>669240</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>417240</xdr:rowOff>
+      <xdr:rowOff>483840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -397,8 +397,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="885240" y="2182680"/>
-          <a:ext cx="348840" cy="320400"/>
+          <a:off x="1121040" y="1093320"/>
+          <a:ext cx="348480" cy="320040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -414,15 +414,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>85320</xdr:colOff>
+      <xdr:colOff>242640</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>96840</xdr:rowOff>
+      <xdr:rowOff>230760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>538920</xdr:colOff>
+      <xdr:colOff>695880</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>417240</xdr:rowOff>
+      <xdr:rowOff>550800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -435,8 +435,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="885600" y="2944800"/>
-          <a:ext cx="453600" cy="320400"/>
+          <a:off x="1042920" y="1922400"/>
+          <a:ext cx="453240" cy="320040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -451,16 +451,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>796680</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1059840</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>311040</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>105120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>335880</xdr:colOff>
+      <xdr:colOff>650160</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>318960</xdr:rowOff>
+      <xdr:rowOff>425160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -473,8 +473,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="796680" y="3907800"/>
-          <a:ext cx="339480" cy="320400"/>
+          <a:off x="1111320" y="2573280"/>
+          <a:ext cx="339120" cy="320040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -679,8 +679,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="11" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="26" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="11" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -759,21 +758,21 @@
       <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="0"/>
-      <c r="AA1" s="0"/>
-      <c r="AB1" s="0"/>
-      <c r="AC1" s="0"/>
-      <c r="AD1" s="0"/>
-      <c r="AE1" s="0"/>
-      <c r="AF1" s="0"/>
-      <c r="AG1" s="0"/>
-      <c r="AH1" s="0"/>
-      <c r="AI1" s="0"/>
-      <c r="AJ1" s="0"/>
-      <c r="AK1" s="0"/>
-      <c r="AL1" s="0"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="149.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
@@ -913,7 +912,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="83.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>42</v>
       </c>

--- a/public/files/products_export.xlsx
+++ b/public/files/products_export.xlsx
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
   <si>
     <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image</t>
   </si>
   <si>
     <t xml:space="preserve">Sort Id</t>
@@ -331,163 +328,6 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>315000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>57240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>734760</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>600480</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="image2.png 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="21464400">
-          <a:off x="1115280" y="247320"/>
-          <a:ext cx="419760" cy="543240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>320760</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>669240</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>483840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1121040" y="1093320"/>
-          <a:ext cx="348480" cy="320040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>242640</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>230760</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>695880</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>550800</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image4.png"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1042920" y="1922400"/>
-          <a:ext cx="453240" cy="320040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>311040</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>105120</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>650160</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>425160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image3.png"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1111320" y="2573280"/>
-          <a:ext cx="339120" cy="320040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -670,16 +510,15 @@
   <dimension ref="A1:AL5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="58.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="58.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -755,9 +594,7 @@
       <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -770,20 +607,23 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
+      <c r="AL1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="58.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -792,41 +632,41 @@
       <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>30</v>
+      <c r="I2" s="3" t="n">
+        <v>29384</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>29384</v>
-      </c>
-      <c r="K2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>12</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="N2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" s="3" t="s">
+      <c r="S2" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T2" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>33</v>
+      <c r="U2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>4</v>
@@ -834,21 +674,21 @@
       <c r="W2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="X2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>31</v>
+      <c r="X2" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -860,69 +700,69 @@
       <c r="H3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
+      <c r="I3" s="3" t="n">
+        <v>38575</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>38575</v>
-      </c>
-      <c r="K3" s="3" t="n">
         <v>279.99</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="K3" s="2" t="n">
         <v>213</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="R3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="T3" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>33</v>
+      <c r="T3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="X3" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>40</v>
+      <c r="X3" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="7"/>
       <c r="F4" s="3" t="s">
         <v>44</v>
       </c>
@@ -932,44 +772,44 @@
       <c r="H4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>47</v>
+      <c r="I4" s="3" t="n">
+        <v>8585858</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>8585858</v>
-      </c>
-      <c r="K4" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>12</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>31</v>
+      <c r="N4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="3" t="n">
         <v>9</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>33</v>
+      <c r="T4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>5</v>
@@ -977,83 +817,80 @@
       <c r="W4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>40</v>
+      <c r="X4" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="47" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>54</v>
+      <c r="I5" s="3" t="n">
+        <v>75758858</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>75758858</v>
-      </c>
-      <c r="K5" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="L5" s="5" t="n">
-        <f aca="false">K2*5%</f>
+      <c r="K5" s="5" t="n">
+        <f aca="false">J2*5%</f>
         <v>5</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>40</v>
+      <c r="N5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="3" t="n">
         <v>9</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="U5" s="3" t="s">
-        <v>33</v>
+      <c r="T5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="X5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Y5" s="3" t="s">
-        <v>31</v>
+      <c r="X5" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1064,6 +901,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>